--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_390_R42.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_390_R42.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5967</v>
+        <v>10.2647</v>
       </c>
       <c r="E2" t="n">
-        <v>9.734</v>
+        <v>10.2728</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1373</v>
+        <v>-0.008</v>
       </c>
       <c r="G2" t="n">
         <v>10.1394</v>
@@ -610,13 +610,13 @@
         <v>1.5923</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4526</v>
+        <v>0.2155</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1555</v>
+        <v>0.3833</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2971</v>
+        <v>-0.1678</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5451</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.4146</v>
+        <v>7.457</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6474</v>
+        <v>4.8514</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7672</v>
+        <v>2.6056</v>
       </c>
       <c r="G3" t="n">
         <v>4.6678</v>
@@ -688,13 +688,13 @@
         <v>1.5923</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6995</v>
+        <v>1.7419</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2447</v>
+        <v>1.4488</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4547</v>
+        <v>0.2931</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5451</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2037</v>
+        <v>4.8125</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7534</v>
+        <v>3.1036</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4503</v>
+        <v>1.7089</v>
       </c>
       <c r="G4" t="n">
         <v>2.8382</v>
@@ -766,13 +766,13 @@
         <v>1.1374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.498</v>
+        <v>0.1107</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6344</v>
+        <v>-0.2842</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1364</v>
+        <v>0.395</v>
       </c>
       <c r="V4" t="n">
         <v>1.8635</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8923</v>
+        <v>4.3664</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0484</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8438</v>
+        <v>3.7792</v>
       </c>
       <c r="G5" t="n">
         <v>0.7095</v>
@@ -844,13 +844,13 @@
         <v>1.8198</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0463</v>
+        <v>1.5204</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2874</v>
+        <v>0.8262</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7588</v>
+        <v>0.6942</v>
       </c>
       <c r="V5" t="n">
         <v>0.3167</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9445</v>
+        <v>3.481</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1923</v>
+        <v>2.4404</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7522</v>
+        <v>1.0405</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.209</v>
+        <v>2.167</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7959000000000001</v>
+        <v>1.2969</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5868</v>
+        <v>0.8701</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7298</v>
+        <v>2.3026</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8165</v>
+        <v>1.777</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0867</v>
+        <v>0.5256</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5207000000000001</v>
+        <v>-0.1356</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0206</v>
+        <v>-0.4801</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5001</v>
+        <v>0.3445</v>
       </c>
       <c r="P6" t="n">
         <v>1.3648</v>
@@ -922,28 +922,28 @@
         <v>1.3648</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7887</v>
+        <v>0.6525</v>
       </c>
       <c r="T6" t="n">
-        <v>0.922</v>
+        <v>0.1378</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8667</v>
+        <v>0.5147</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.7034</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.7034</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5866</v>
+        <v>2.4129</v>
       </c>
       <c r="E7" t="n">
-        <v>1.74</v>
+        <v>-0.2747</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8466</v>
+        <v>2.6876</v>
       </c>
       <c r="G7" t="n">
-        <v>2.167</v>
+        <v>-0.209</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2969</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8701</v>
+        <v>0.5868</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3026</v>
+        <v>-0.7298</v>
       </c>
       <c r="K7" t="n">
-        <v>1.777</v>
+        <v>-0.8165</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5256</v>
+        <v>0.0867</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1356</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4801</v>
+        <v>0.0206</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3445</v>
+        <v>0.5001</v>
       </c>
       <c r="P7" t="n">
         <v>1.3648</v>
@@ -1000,22 +1000,22 @@
         <v>1.3648</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2418</v>
+        <v>1.2571</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5626</v>
+        <v>0.4551</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3208</v>
+        <v>0.802</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7034</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8995</v>
+        <v>2.0288</v>
       </c>
       <c r="E8" t="n">
         <v>1.5633</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3363</v>
+        <v>0.4655</v>
       </c>
       <c r="G8" t="n">
         <v>1.957</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0575</v>
+        <v>0.0718</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1437</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0862</v>
+        <v>0.2155</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5354</v>
+        <v>0.6917</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5587</v>
+        <v>0.7473</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0233</v>
+        <v>-0.0556</v>
       </c>
       <c r="G9" t="n">
         <v>1.5992</v>
@@ -1156,13 +1156,13 @@
         <v>1.3648</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2012</v>
+        <v>-0.0449</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0837</v>
+        <v>0.1049</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1175</v>
+        <v>-0.1498</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0901</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9357</v>
+        <v>-0.8945</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2864</v>
+        <v>-1.417</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3507</v>
+        <v>0.5225</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0961</v>
+        <v>2.6324</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3634</v>
+        <v>0.1564</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4595</v>
+        <v>2.476</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7836</v>
+        <v>2.1566</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1916</v>
+        <v>-0.3143</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.592</v>
+        <v>2.4709</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3124</v>
+        <v>0.4758</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5551</v>
+        <v>0.4707</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8675</v>
+        <v>0.0051</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4549</v>
+        <v>-2.0473</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.4121</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4549</v>
+        <v>1.3648</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2946</v>
+        <v>0.1555</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5028</v>
+        <v>-0.1615</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2082</v>
+        <v>0.317</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.6352</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.6352</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0526</v>
+        <v>-1.0003</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1892</v>
+        <v>-1.2864</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1366</v>
+        <v>0.2861</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6324</v>
+        <v>-1.0961</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1564</v>
+        <v>0.3634</v>
       </c>
       <c r="I11" t="n">
-        <v>2.476</v>
+        <v>-1.4595</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1566</v>
+        <v>-0.7836</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3143</v>
+        <v>-0.1916</v>
       </c>
       <c r="L11" t="n">
-        <v>2.4709</v>
+        <v>-0.592</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4758</v>
+        <v>-0.3124</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4707</v>
+        <v>0.5551</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0051</v>
+        <v>-0.8675</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0473</v>
+        <v>0.4549</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4121</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3648</v>
+        <v>0.4549</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0026</v>
+        <v>-0.3592</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9337</v>
+        <v>-0.5028</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9312</v>
+        <v>0.1436</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6352</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1966</v>
+        <v>-2.3977</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6211</v>
+        <v>-1.8545</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5755</v>
+        <v>-0.5432</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4816</v>
@@ -1390,13 +1390,13 @@
         <v>0.4549</v>
       </c>
       <c r="S12" t="n">
-        <v>0.285</v>
+        <v>0.0839</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3473</v>
+        <v>0.1138</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0623</v>
+        <v>-0.03</v>
       </c>
       <c r="V12" t="n">
         <v>0.5451</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.846</v>
+        <v>-2.8209</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7202</v>
+        <v>-0.9537</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1258</v>
+        <v>-1.8672</v>
       </c>
       <c r="G13" t="n">
         <v>-1.375</v>
@@ -1468,13 +1468,13 @@
         <v>1.1374</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2226</v>
+        <v>-0.1975</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.1615</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2946</v>
+        <v>-0.036</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2485</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.0424</v>
+        <v>28.40159999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>17.4206</v>
+        <v>17.77969999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>10.6218</v>
+        <v>10.6219</v>
       </c>
       <c r="G14" t="n">
         <v>20.5488</v>
@@ -1534,7 +1534,7 @@
         <v>-0.04709999999999984</v>
       </c>
       <c r="O14" t="n">
-        <v>1.7481</v>
+        <v>1.748099999999999</v>
       </c>
       <c r="P14" t="n">
         <v>5.6866</v>
@@ -1546,10 +1546,10 @@
         <v>13.6482</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8486</v>
+        <v>5.2077</v>
       </c>
       <c r="T14" t="n">
-        <v>1.857</v>
+        <v>2.2162</v>
       </c>
       <c r="U14" t="n">
         <v>2.9915</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.1809</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1779</v>
+        <v>1.7109</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5564</v>
+        <v>-1.53</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2415</v>
@@ -1624,13 +1624,13 @@
         <v>0.6824</v>
       </c>
       <c r="S15" t="n">
-        <v>0.06950000000000001</v>
+        <v>-0.3711</v>
       </c>
       <c r="T15" t="n">
-        <v>0.06</v>
+        <v>-0.407</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0095</v>
+        <v>0.0358</v>
       </c>
       <c r="V15" t="n">
         <v>1.2485</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4298</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1537</v>
+        <v>-0.5039</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2761</v>
+        <v>-0.1791</v>
       </c>
       <c r="G16" t="n">
         <v>-2.3149</v>
@@ -1702,13 +1702,13 @@
         <v>0.4549</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3401</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2755</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0646</v>
+        <v>0.1616</v>
       </c>
       <c r="V16" t="n">
         <v>1.0901</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. MADAR</t>
+          <t>K. EDWARDS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5056</v>
+        <v>-1.018</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7322</v>
+        <v>0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2267</v>
+        <v>-1.108</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7561</v>
+        <v>-1.3053</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7628</v>
+        <v>-0.7573</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0066</v>
+        <v>-0.5481</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9604</v>
+        <v>0.4311</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5565</v>
+        <v>0.0173</v>
       </c>
       <c r="L17" t="n">
-        <v>0.596</v>
+        <v>0.4138</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7957</v>
+        <v>-1.7364</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2063</v>
+        <v>-0.7745</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5894</v>
+        <v>-0.9619</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6824</v>
+        <v>0.4549</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0.4549</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8429</v>
+        <v>-0.1676</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2755</v>
+        <v>-0.3411</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5674</v>
+        <v>0.1735</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0901</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0901</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. EDWARDS</t>
+          <t>Y. MADAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8959</v>
+        <v>-1.082</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1435</v>
+        <v>-1.0824</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7524</v>
+        <v>0.0004</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3053</v>
+        <v>-1.7561</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7573</v>
+        <v>-1.7628</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5481</v>
+        <v>0.0066</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4311</v>
+        <v>-0.9604</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>-1.5565</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4138</v>
+        <v>0.596</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7364</v>
+        <v>-0.7957</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7745</v>
+        <v>-0.2063</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9619</v>
+        <v>-0.5894</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4549</v>
+        <v>-0.6824</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R18" t="n">
         <v>0.4549</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0455</v>
+        <v>0.2664</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5746</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5291</v>
+        <v>0.3412</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>V. MICIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7712</v>
+        <v>-1.4963</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6287</v>
+        <v>-2.1686</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.4</v>
+        <v>0.6723</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.384</v>
+        <v>-0.4282</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1688</v>
+        <v>1.5554</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5528</v>
+        <v>-1.9836</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6943</v>
+        <v>-0.5315</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5453</v>
+        <v>1.2403</v>
       </c>
       <c r="L19" t="n">
-        <v>0.149</v>
+        <v>-1.7718</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0783</v>
+        <v>0.1033</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3765</v>
+        <v>0.315</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7019</v>
+        <v>-0.2117</v>
       </c>
       <c r="P19" t="n">
         <v>-0.4549</v>
@@ -1936,28 +1936,28 @@
         <v>0.6824</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2489</v>
+        <v>-0.2964</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1199</v>
+        <v>-0.4997</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3689</v>
+        <v>0.2033</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3167</v>
+        <v>-0.3167</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9519</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6352</v>
+        <v>-0.3167</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. MICIC</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8728</v>
+        <v>-1.9922</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5188</v>
+        <v>2.2785</v>
       </c>
       <c r="F20" t="n">
-        <v>0.646</v>
+        <v>-4.2707</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4282</v>
+        <v>-1.384</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5554</v>
+        <v>0.1688</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9836</v>
+        <v>-1.5528</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5315</v>
+        <v>1.6943</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2403</v>
+        <v>1.5453</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.7718</v>
+        <v>0.149</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1033</v>
+        <v>-3.0783</v>
       </c>
       <c r="N20" t="n">
-        <v>0.315</v>
+        <v>-1.3765</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2117</v>
+        <v>-1.7019</v>
       </c>
       <c r="P20" t="n">
         <v>-0.4549</v>
@@ -2014,22 +2014,22 @@
         <v>0.6824</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.4699</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8499</v>
+        <v>-0.2303</v>
       </c>
       <c r="U20" t="n">
-        <v>0.177</v>
+        <v>-0.2396</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3167</v>
+        <v>0.3167</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.9519</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3167</v>
+        <v>-1.6352</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9953</v>
+        <v>-2.9234</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.921</v>
+        <v>-0.6875</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0742</v>
+        <v>-2.2358</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2712</v>
@@ -2092,13 +2092,13 @@
         <v>0.9099</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5867</v>
+        <v>-0.5148</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4308</v>
+        <v>-0.1973</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1559</v>
+        <v>-0.3175</v>
       </c>
       <c r="V21" t="n">
         <v>1.0901</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7519</v>
+        <v>-3.8707</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8119</v>
+        <v>-1.345</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.94</v>
+        <v>-2.5257</v>
       </c>
       <c r="G22" t="n">
         <v>1.2028</v>
@@ -2170,13 +2170,13 @@
         <v>0.4549</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0185</v>
+        <v>-1.1374</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6344</v>
+        <v>-0.1675</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3841</v>
+        <v>-0.9699</v>
       </c>
       <c r="V22" t="n">
         <v>0.1583</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0971</v>
+        <v>-4.4205</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8712</v>
+        <v>-1.7449</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2259</v>
+        <v>-2.6756</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8625</v>
+        <v>-3.504</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5736</v>
+        <v>-1.9833</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2888</v>
+        <v>-1.5207</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1712</v>
+        <v>-1.1765</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.283</v>
+        <v>-1.2632</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1118</v>
+        <v>0.0867</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6913</v>
+        <v>-2.3276</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2907</v>
+        <v>-0.7201</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4006</v>
+        <v>-1.6074</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2275</v>
+        <v>0.9099</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0.9099</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9171</v>
+        <v>-0.7363</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5626</v>
+        <v>-0.5685</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3545</v>
+        <v>-0.1678</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0901</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1468</v>
+        <v>-4.611</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8428</v>
+        <v>-3.6377</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3041</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.6839</v>
+        <v>-2.8625</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9154</v>
+        <v>-2.5736</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7685</v>
+        <v>-0.2888</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.245</v>
+        <v>-2.1712</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5558</v>
+        <v>-2.283</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.6892</v>
+        <v>0.1118</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4389</v>
+        <v>-0.6913</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3596</v>
+        <v>-0.2907</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0793</v>
+        <v>-0.4006</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9099</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2747</v>
+        <v>-1.1374</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3648</v>
+        <v>0.9099</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.431</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1319</v>
+        <v>-0.3291</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2301</v>
+        <v>-0.1018</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5451</v>
+        <v>-1.0901</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5451</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1975</v>
+        <v>-5.348</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9784</v>
+        <v>-4.0762</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2191</v>
+        <v>-1.2718</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.504</v>
+        <v>-4.6839</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.9833</v>
+        <v>-1.9154</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5207</v>
+        <v>-2.7685</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.1765</v>
+        <v>-2.245</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.2632</v>
+        <v>-0.5558</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0867</v>
+        <v>-1.6892</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.3276</v>
+        <v>-2.4389</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7201</v>
+        <v>-1.3596</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.6074</v>
+        <v>-1.0793</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9099</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.2747</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9099</v>
+        <v>1.3648</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5132</v>
+        <v>-0.2993</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.1015</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7113</v>
+        <v>-0.1977</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0901</v>
+        <v>0.5451</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-28.0424</v>
+        <v>-27.2642</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.1669</v>
+        <v>-11.1668</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.8755</v>
+        <v>-16.0973</v>
       </c>
       <c r="G26" t="n">
         <v>-20.5488</v>
@@ -2458,7 +2458,7 @@
         <v>-1.7009</v>
       </c>
       <c r="K26" t="n">
-        <v>0.04699999999999993</v>
+        <v>0.04699999999999982</v>
       </c>
       <c r="L26" t="n">
         <v>-1.7481</v>
@@ -2482,13 +2482,13 @@
         <v>7.9613</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.848400000000001</v>
+        <v>-4.0705</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.9914</v>
+        <v>-2.9916</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.8572</v>
+        <v>-1.0789</v>
       </c>
       <c r="V26" t="n">
         <v>3.042</v>
